--- a/import/Корректировки/4 неделя/21.09.xlsx
+++ b/import/Корректировки/4 неделя/21.09.xlsx
@@ -1585,7 +1585,9 @@
       <c r="E31" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F31" s="7"/>
+      <c r="F31" s="7">
+        <v>3</v>
+      </c>
       <c r="G31" s="8"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
